--- a/01_data_model/01_code_lists/03_country_codes/input/countrynis_natlty.xlsx
+++ b/01_data_model/01_code_lists/03_country_codes/input/countrynis_natlty.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vanniejo\Documents_local\01_dataplatform\021_SVbevraging\01_code\01_data_model\01_code_lists\03_country_codes\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22BB37CF-9B51-44E6-8E96-3320156E2214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD811C09-2775-44F0-9914-2284E2C5390A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="998">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1317" uniqueCount="1027">
   <si>
     <t>label_nl</t>
   </si>
@@ -3027,6 +3027,93 @@
   </si>
   <si>
     <t>Refugee</t>
+  </si>
+  <si>
+    <t>nog niet definitief bewezen</t>
+  </si>
+  <si>
+    <t>van Pakistaanse herkomst</t>
+  </si>
+  <si>
+    <t>van Tanzaniaanse herkomst</t>
+  </si>
+  <si>
+    <t>van Palestijnse herkomst</t>
+  </si>
+  <si>
+    <t>van Srilankaanse herkomst</t>
+  </si>
+  <si>
+    <t>van Albanese herkomst</t>
+  </si>
+  <si>
+    <t>van Oegandese herkomst</t>
+  </si>
+  <si>
+    <t>van Congolese herkomst</t>
+  </si>
+  <si>
+    <t>van Ethiopische herkomst</t>
+  </si>
+  <si>
+    <t>pas encore définitivement prouvé</t>
+  </si>
+  <si>
+    <t>d'origine pakistanaise</t>
+  </si>
+  <si>
+    <t>d'origine tanzanienne</t>
+  </si>
+  <si>
+    <t>d'origine sri-lankaise</t>
+  </si>
+  <si>
+    <t>d'origine albanaise</t>
+  </si>
+  <si>
+    <t>d'origine ougandaise</t>
+  </si>
+  <si>
+    <t>d'origine congolaise</t>
+  </si>
+  <si>
+    <t>d'origine éthiopienne</t>
+  </si>
+  <si>
+    <t>not yet definitively proven</t>
+  </si>
+  <si>
+    <t>of Pakistani origin</t>
+  </si>
+  <si>
+    <t>of Tanzanian origin</t>
+  </si>
+  <si>
+    <t>of Sri Lankan origin</t>
+  </si>
+  <si>
+    <t>of Albanian origin</t>
+  </si>
+  <si>
+    <t>of Ugandan origin</t>
+  </si>
+  <si>
+    <t>of Congolese origin</t>
+  </si>
+  <si>
+    <t>of Ethiopian origin</t>
+  </si>
+  <si>
+    <t>UNKNOWN</t>
+  </si>
+  <si>
+    <t>Van Oekraïense herkomst</t>
+  </si>
+  <si>
+    <t>d'origine ukrainienne</t>
+  </si>
+  <si>
+    <t>of Ukrainian origin</t>
   </si>
 </sst>
 </file>
@@ -3379,7 +3466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E319"/>
+  <dimension ref="A1:E329"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -3419,6 +3506,9 @@
       <c r="D2" t="s">
         <v>5</v>
       </c>
+      <c r="E2" t="s">
+        <v>1023</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
@@ -8516,158 +8606,161 @@
       <c r="D302" t="s">
         <v>997</v>
       </c>
+      <c r="E302" t="s">
+        <v>1023</v>
+      </c>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303">
-        <v>8788</v>
+        <v>8711</v>
       </c>
       <c r="B303" t="s">
-        <v>959</v>
+        <v>943</v>
       </c>
       <c r="C303" t="s">
-        <v>971</v>
+        <v>944</v>
       </c>
       <c r="D303" t="s">
-        <v>982</v>
+        <v>945</v>
       </c>
       <c r="E303" t="s">
-        <v>354</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304">
-        <v>8785</v>
+        <v>8751</v>
       </c>
       <c r="B304" t="s">
-        <v>960</v>
+        <v>1003</v>
       </c>
       <c r="C304" t="s">
-        <v>972</v>
+        <v>1011</v>
       </c>
       <c r="D304" t="s">
-        <v>983</v>
+        <v>1019</v>
       </c>
       <c r="E304" t="s">
-        <v>331</v>
+        <v>6</v>
       </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305">
-        <v>8822</v>
+        <v>8760</v>
       </c>
       <c r="B305" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="C305" t="s">
-        <v>973</v>
+        <v>978</v>
       </c>
       <c r="D305" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
       <c r="E305" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306">
-        <v>8873</v>
+        <v>8776</v>
       </c>
       <c r="B306" t="s">
-        <v>962</v>
+        <v>1004</v>
       </c>
       <c r="C306" t="s">
-        <v>974</v>
+        <v>1012</v>
       </c>
       <c r="D306" t="s">
-        <v>985</v>
+        <v>1020</v>
       </c>
       <c r="E306" t="s">
-        <v>547</v>
+        <v>473</v>
       </c>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307">
-        <v>8782</v>
+        <v>8777</v>
       </c>
       <c r="B307" t="s">
-        <v>963</v>
+        <v>999</v>
       </c>
       <c r="C307" t="s">
-        <v>975</v>
+        <v>1008</v>
       </c>
       <c r="D307" t="s">
-        <v>986</v>
+        <v>1016</v>
       </c>
       <c r="E307" t="s">
-        <v>250</v>
+        <v>348</v>
       </c>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308">
-        <v>8855</v>
+        <v>8782</v>
       </c>
       <c r="B308" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="C308" t="s">
-        <v>993</v>
+        <v>975</v>
       </c>
       <c r="D308" t="s">
-        <v>994</v>
+        <v>986</v>
       </c>
       <c r="E308" t="s">
-        <v>317</v>
+        <v>250</v>
       </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309">
-        <v>8821</v>
+        <v>8785</v>
       </c>
       <c r="B309" t="s">
-        <v>965</v>
+        <v>960</v>
       </c>
       <c r="C309" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="D309" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="E309" t="s">
-        <v>492</v>
+        <v>331</v>
       </c>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310">
-        <v>8802</v>
+        <v>8787</v>
       </c>
       <c r="B310" t="s">
-        <v>966</v>
+        <v>1001</v>
       </c>
       <c r="C310" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="D310" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="E310" t="s">
-        <v>449</v>
+        <v>386</v>
       </c>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311">
-        <v>8760</v>
+        <v>8788</v>
       </c>
       <c r="B311" t="s">
-        <v>967</v>
+        <v>959</v>
       </c>
       <c r="C311" t="s">
-        <v>978</v>
+        <v>971</v>
       </c>
       <c r="D311" t="s">
-        <v>989</v>
+        <v>982</v>
       </c>
       <c r="E311" t="s">
-        <v>327</v>
+        <v>354</v>
       </c>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
@@ -8689,109 +8782,297 @@
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313">
-        <v>8819</v>
+        <v>8800</v>
       </c>
       <c r="B313" t="s">
-        <v>969</v>
+        <v>1006</v>
       </c>
       <c r="C313" t="s">
-        <v>980</v>
+        <v>1014</v>
       </c>
       <c r="D313" t="s">
-        <v>991</v>
+        <v>1022</v>
       </c>
       <c r="E313" t="s">
-        <v>302</v>
+        <v>437</v>
       </c>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314">
-        <v>8902</v>
+        <v>8802</v>
       </c>
       <c r="B314" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="C314" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="D314" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="E314" t="s">
-        <v>386</v>
+        <v>449</v>
       </c>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315">
-        <v>8711</v>
+        <v>8812</v>
       </c>
       <c r="B315" t="s">
-        <v>943</v>
+        <v>1000</v>
       </c>
       <c r="C315" t="s">
-        <v>944</v>
+        <v>1009</v>
       </c>
       <c r="D315" t="s">
-        <v>945</v>
+        <v>1017</v>
+      </c>
+      <c r="E315" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316">
-        <v>8888</v>
+        <v>8819</v>
       </c>
       <c r="B316" t="s">
-        <v>943</v>
+        <v>969</v>
       </c>
       <c r="C316" t="s">
-        <v>944</v>
+        <v>980</v>
       </c>
       <c r="D316" t="s">
-        <v>945</v>
+        <v>991</v>
+      </c>
+      <c r="E316" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317">
-        <v>8900</v>
+        <v>8821</v>
       </c>
       <c r="B317" t="s">
-        <v>946</v>
+        <v>965</v>
       </c>
       <c r="C317" t="s">
-        <v>947</v>
+        <v>976</v>
       </c>
       <c r="D317" t="s">
-        <v>948</v>
+        <v>987</v>
+      </c>
+      <c r="E317" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318">
-        <v>8998</v>
+        <v>8822</v>
       </c>
       <c r="B318" t="s">
-        <v>943</v>
+        <v>961</v>
       </c>
       <c r="C318" t="s">
-        <v>944</v>
+        <v>973</v>
       </c>
       <c r="D318" t="s">
-        <v>945</v>
+        <v>984</v>
+      </c>
+      <c r="E318" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319">
+        <v>8839</v>
+      </c>
+      <c r="B319" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C319" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D319" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E319" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A320">
+        <v>8855</v>
+      </c>
+      <c r="B320" t="s">
+        <v>964</v>
+      </c>
+      <c r="C320" t="s">
+        <v>993</v>
+      </c>
+      <c r="D320" t="s">
+        <v>994</v>
+      </c>
+      <c r="E320" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A321">
+        <v>8859</v>
+      </c>
+      <c r="B321" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C321" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D321" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E321" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A322">
+        <v>8772</v>
+      </c>
+      <c r="B322" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C322" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D322" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E322" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A323">
+        <v>8873</v>
+      </c>
+      <c r="B323" t="s">
+        <v>962</v>
+      </c>
+      <c r="C323" t="s">
+        <v>974</v>
+      </c>
+      <c r="D323" t="s">
+        <v>985</v>
+      </c>
+      <c r="E323" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A324">
+        <v>8888</v>
+      </c>
+      <c r="B324" t="s">
+        <v>943</v>
+      </c>
+      <c r="C324" t="s">
+        <v>944</v>
+      </c>
+      <c r="D324" t="s">
+        <v>945</v>
+      </c>
+      <c r="E324" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A325">
+        <v>8900</v>
+      </c>
+      <c r="B325" t="s">
+        <v>946</v>
+      </c>
+      <c r="C325" t="s">
+        <v>947</v>
+      </c>
+      <c r="D325" t="s">
+        <v>948</v>
+      </c>
+      <c r="E325" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A326">
+        <v>8901</v>
+      </c>
+      <c r="B326" t="s">
+        <v>998</v>
+      </c>
+      <c r="C326" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D326" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E326" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A327">
+        <v>8902</v>
+      </c>
+      <c r="B327" t="s">
+        <v>970</v>
+      </c>
+      <c r="C327" t="s">
+        <v>981</v>
+      </c>
+      <c r="D327" t="s">
+        <v>992</v>
+      </c>
+      <c r="E327" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A328">
+        <v>8998</v>
+      </c>
+      <c r="B328" t="s">
+        <v>943</v>
+      </c>
+      <c r="C328" t="s">
+        <v>944</v>
+      </c>
+      <c r="D328" t="s">
+        <v>945</v>
+      </c>
+      <c r="E328" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A329">
         <v>8999</v>
       </c>
-      <c r="B319" t="s">
+      <c r="B329" t="s">
         <v>943</v>
       </c>
-      <c r="C319" t="s">
+      <c r="C329" t="s">
         <v>944</v>
       </c>
-      <c r="D319" t="s">
+      <c r="D329" t="s">
         <v>945</v>
       </c>
+      <c r="E329" t="s">
+        <v>1023</v>
+      </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E329">
+    <sortCondition ref="A2:A329"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
